--- a/main.xlsx
+++ b/main.xlsx
@@ -514,18 +514,18 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `Main` class serves as a container for several static utility methods and acts as the entry point for the Java application.</t>
+          <t>The `Main` class serves as the entry point for the application and provides a collection of static utility methods for basic mathematical calculations and console output.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>This class provides basic functionalities through its static methods, which can be called without creating an instance of the class. It includes methods for arithmetic operations, factorial calculation, and printing messages. The class contains the following key methods: - **`public static int add(int a, int b)`** This method takes two integer parameters, `a` and `b`, and returns their sum. It performs a simple addition operation. - **`public static int factorial(int n)`** This method calcula...</t>
+          <t>The `Main` class is a container for several independent, `static` methods. As the methods are static, they can be called directly on the class without needing to create an instance of `Main`. The class demonstrates basic Java functionalities including arithmetic operations, recursion, and console I/O. The class includes the following methods: - `add(int a, int b)`: A simple function that accepts two integer arguments, `a` and `b`, and returns their sum. - `factorial(int n)`: A recursive funct...</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- All methods in this class are `static`, meaning they belong to the class itself and can be invoked directly using the class name (e.g., `Main.add(5, 10)`) without needing to create an object of the `Main` class. - The `factorial` method uses recursion. Providing a very large integer as input may result in a `StackOverflowError` due to excessive recursive calls. - The `main` method is the standard entry point for any executable Java program. **Output Example**: The output shown in the exampl...</t>
+          <t>- All utility methods (`add`, `factorial`, `greet`) are `static` and should be invoked directly on the class, e.g., `Main.add(5, 10)`. - The `factorial` method is implemented recursively. Providing a very large integer as input may lead to a `StackOverflowError` due to deep recursion. - The `main` method is the designated starting point for execution by the Java Virtual Machine (JVM) and is where the program begins.</t>
         </is>
       </c>
     </row>

--- a/main.xlsx
+++ b/main.xlsx
@@ -35,7 +35,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +52,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9E8F5"/>
         <bgColor rgb="00D9E8F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -82,6 +88,12 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -449,14 +461,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
@@ -514,18 +526,158 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `Main` class serves as the entry point for the application and provides a collection of static utility methods for basic mathematical calculations and console output.</t>
+          <t>The `Main` class serves as the entry point for the application and provides a collection of static utility methods for basic mathematical operations and console output.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>The `Main` class is a container for several independent, `static` methods. As the methods are static, they can be called directly on the class without needing to create an instance of `Main`. The class demonstrates basic Java functionalities including arithmetic operations, recursion, and console I/O. The class includes the following methods: - `add(int a, int b)`: A simple function that accepts two integer arguments, `a` and `b`, and returns their sum. - `factorial(int n)`: A recursive funct...</t>
+          <t>The `Main` class is a public class that contains several `static` methods. As these methods are static, they belong to the class itself and can be invoked directly without needing to create an instance of the `Main` class. The class includes functions for addition, factorial calculation, and printing a greeting, along with the standard `main` method that executes the program.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- All utility methods (`add`, `factorial`, `greet`) are `static` and should be invoked directly on the class, e.g., `Main.add(5, 10)`. - The `factorial` method is implemented recursively. Providing a very large integer as input may lead to a `StackOverflowError` due to deep recursion. - The `main` method is the designated starting point for execution by the Java Virtual Machine (JVM) and is where the program begins.</t>
+          <t>- All methods in this class are `static`, so they should be called directly on the `Main` class (e.g., `Main.add(5, 10)`) rather than on an instance of the class. - The `factorial` method is recursive. Providing a very large integer as input may lead to a `StackOverflowError` due to excessive recursion depth. - The `greet` method's output is sent directly to `System.out` and cannot be captured as a return value from the method call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>The `add` function calculates and returns the sum of two integer numbers.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Description | The first integer to be added. | The second integer to be added. |</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>The `add` function is a static method that performs a simple arithmetic addition. It takes two integer parameters, `a` and `b`. The core logic of the function is the expression `a + b`, which computes the sum of the two input values. The resulting integer sum is then returned by the function. Because it is a `static` method, it can be called directly on the `Main` class without needing to create an instance of the class.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>- This function is `static` and should be called on the class itself, for example, `Main.add(5, 10)`. - The function operates on primitive `int` types. Be aware of potential integer overflow if the sum of `a` and `b` exceeds the maximum value for an `int` (`Integer.MAX_VALUE`, which is 2,147,483,647). **Output Example**: A call to `add(15, 7)` would return the integer `22`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>factorial</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>The `factorial` function recursively calculates the factorial of a given non-negative integer.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>- `n`: `int` - The non-negative integer for which to calculate the factorial.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>This function computes the factorial of an integer `n`, which is the product of all positive integers up to `n` (i.e., n!). It employs a recursive approach. The logic is divided into two main parts: 1. **Base Case**: The recursion terminates when the input `n` is less than or equal to 1. In this scenario, the function returns `1`. This is because the factorial of 1 (`1!`) is 1, and by convention, the factorial of 0 (`0!`) is also 1. 2. **Recursive Step**: If `n` is greater than 1, the functio...</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>- The function is designed for non-negative integers. Providing a negative number will result in a `StackOverflowError` due to infinite recursion. - The return type is `int`. Factorial values grow very rapidly. For larger values of `n` (typically `n &gt; 12`), the result will exceed the maximum value of a standard `int`, leading to an integer overflow and an incorrect result. For larger numbers, a `long` or `BigInteger` return type would be more appropriate. **Output Example**: A call to `factor...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>greet</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>The `greet` function prints a personalized greeting message to the standard output console.</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>- `name` (String): The name of the person or entity to be greeted. This string will be incorporated into the output message.</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>This `public static` method is designed to display a simple, formatted greeting. It accepts a single `String` argument named `name`. The core functionality is handled by the `System.out.println()` method, which prints a complete line of text to the console. The text is constructed by concatenating the literal string `"Hello, "`, the value of the `name` parameter, and the literal string `"!"`. For instance, if the `name` parameter is `"Alice"`, the function will print the line `"Hello, Alice!"`.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>- This is a `void` method, meaning it does not return any value. Its only effect is printing to the console. - As a `static` method, it should be called directly on the class, for example, `Main.greet("World")`, rather than on an instance of the `Main` class. - The output is always directed to the standard output stream.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>The `main` function serves as the entry point for the Java application, demonstrating the functionality of the `add`, `factorial`, and `greet` methods by printing their results to the console.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>- `args`: `String[]` - An array of `String` objects that allows passing command-line arguments to the application. This parameter is not utilized within the body of this function.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>The `main` method is the starting point of execution for the Java program. When the program is run, the Java Virtual Machine (JVM) calls this method. The method performs the following operations in sequence: 1. It calls the `add(5, 10)` method to calculate the sum of two integers. The result is concatenated with the string `"Sum: "` and printed to the standard output console. 2. It calls the `factorial(5)` method to compute the factorial of the number 5. The result is then concatenated with t...</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>- The `main` method must have the exact signature `public static void main(String[] args)` to be recognized as the application's entry point by the JVM. - This method is not intended to be called directly from other parts of the code; it is invoked by the JVM when the program starts. - The `args` parameter can be used to provide configuration or data to the program at runtime from the command line, although it is unused in this specific implementation.</t>
         </is>
       </c>
     </row>

--- a/main.xlsx
+++ b/main.xlsx
@@ -526,18 +526,18 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `Main` class serves as the entry point for the application and provides a collection of static utility methods for basic mathematical operations and console output.</t>
+          <t>The `Main` class serves as a container for several static utility methods and includes the main entry point for the Java application.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>The `Main` class is a public class that contains several `static` methods. As these methods are static, they belong to the class itself and can be invoked directly without needing to create an instance of the `Main` class. The class includes functions for addition, factorial calculation, and printing a greeting, along with the standard `main` method that executes the program.</t>
+          <t>The `Main` class is designed as a utility class containing static methods, meaning they can be called directly on the class without needing to create an instance. It demonstrates basic programming concepts through its methods and serves as the executable entry point for the program. The class includes the following static methods: **`public static int add(int a, int b)`** This method takes two integer parameters, `a` and `b`, and returns their sum. It performs a simple addition operation. **`...</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- All methods in this class are `static`, so they should be called directly on the `Main` class (e.g., `Main.add(5, 10)`) rather than on an instance of the class. - The `factorial` method is recursive. Providing a very large integer as input may lead to a `StackOverflowError` due to excessive recursion depth. - The `greet` method's output is sent directly to `System.out` and cannot be captured as a return value from the method call.</t>
+          <t>- All methods in this class are `static`, so they should be invoked directly on the class itself (e.g., `Main.add(x, y)`), not on an instance of the class. - The `factorial` method uses recursion. Providing a very large integer as input may lead to a `java.lang.StackOverflowError`. - The `main` method is the standard entry point for any Java application and is used here to demonstrate the functionality of the other methods.</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `add` function calculates and returns the sum of two integer numbers.</t>
+          <t>The `add` function computes the sum of two integer numbers.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -567,12 +567,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>The `add` function is a static method that performs a simple arithmetic addition. It takes two integer parameters, `a` and `b`. The core logic of the function is the expression `a + b`, which computes the sum of the two input values. The resulting integer sum is then returned by the function. Because it is a `static` method, it can be called directly on the `Main` class without needing to create an instance of the class.</t>
+          <t>The `add` function is a `public static` method that takes two integer parameters, `a` and `b`. It performs a standard arithmetic addition operation on these two integers. The core logic is simply `return a + b;`, which calculates the sum and immediately returns the resulting integer value. Because it is a `static` method, it can be called directly on the `Main` class without needing to create an object instance.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- This function is `static` and should be called on the class itself, for example, `Main.add(5, 10)`. - The function operates on primitive `int` types. Be aware of potential integer overflow if the sum of `a` and `b` exceeds the maximum value for an `int` (`Integer.MAX_VALUE`, which is 2,147,483,647). **Output Example**: A call to `add(15, 7)` would return the integer `22`.</t>
+          <t>- As a `static` method, it should be invoked using the class name, for example, `Main.add(5, 10)`. - The function operates on primitive `int` types. Be aware of potential integer overflow if the sum of `a` and `b` exceeds the maximum value for an `int` (`Integer.MAX_VALUE`) or falls below the minimum value (`Integer.MIN_VALUE`). - The function does not perform any null checks or input validation. **Output Example**: A single integer representing the sum. `15`</t>
         </is>
       </c>
     </row>
@@ -597,17 +597,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>- `n`: `int` - The non-negative integer for which to calculate the factorial.</t>
+          <t>- `n`: The non-negative integer for which the factorial will be calculated.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function computes the factorial of an integer `n`, which is the product of all positive integers up to `n` (i.e., n!). It employs a recursive approach. The logic is divided into two main parts: 1. **Base Case**: The recursion terminates when the input `n` is less than or equal to 1. In this scenario, the function returns `1`. This is because the factorial of 1 (`1!`) is 1, and by convention, the factorial of 0 (`0!`) is also 1. 2. **Recursive Step**: If `n` is greater than 1, the functio...</t>
+          <t>This function computes the factorial of a number `n`, which is the product of all positive integers up to `n` (n!). It employs a recursive approach to solve the problem. The logic follows two main paths: 1. **Base Case**: If the input `n` is less than or equal to 1, the function returns `1`. This is because the factorial of 0 (0!) and 1 (1!) are both defined as 1. This condition serves as the termination point for the recursion. 2. **Recursive Step**: If `n` is greater than 1, the function re...</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- The function is designed for non-negative integers. Providing a negative number will result in a `StackOverflowError` due to infinite recursion. - The return type is `int`. Factorial values grow very rapidly. For larger values of `n` (typically `n &gt; 12`), the result will exceed the maximum value of a standard `int`, leading to an integer overflow and an incorrect result. For larger numbers, a `long` or `BigInteger` return type would be more appropriate. **Output Example**: A call to `factor...</t>
+          <t>- The function is intended for non-negative integers. Providing a negative integer will cause infinite recursion, leading to a `StackOverflowError`. - The return type is `int`. Factorial values grow very rapidly. The largest factorial that can be stored in a standard 32-bit signed `int` is `12!`. Any input greater than 12 will result in an integer overflow, producing an incorrect value. For larger numbers, a data type like `long` or `BigInteger` would be required. **Output Example**: A call t...</t>
         </is>
       </c>
     </row>
@@ -632,17 +632,17 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>- `name` (String): The name of the person or entity to be greeted. This string will be incorporated into the output message.</t>
+          <t>- `name` (String): The name of the person or entity to be greeted.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>This `public static` method is designed to display a simple, formatted greeting. It accepts a single `String` argument named `name`. The core functionality is handled by the `System.out.println()` method, which prints a complete line of text to the console. The text is constructed by concatenating the literal string `"Hello, "`, the value of the `name` parameter, and the literal string `"!"`. For instance, if the `name` parameter is `"Alice"`, the function will print the line `"Hello, Alice!"`.</t>
+          <t>The `greet` function is a `public static` method, meaning it can be called directly on the `Main` class without needing to create an instance of the class. It is designed to perform a simple action: displaying a greeting. The function accepts a single parameter, `name`, which is a `String`. It then uses the `System.out.println()` method to print a formatted string to the console. The output string is constructed by concatenating the literal string `"Hello, "`, the value passed in the `name` p...</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>- This is a `void` method, meaning it does not return any value. Its only effect is printing to the console. - As a `static` method, it should be called directly on the class, for example, `Main.greet("World")`, rather than on an instance of the `Main` class. - The output is always directed to the standard output stream.</t>
+          <t>- This function prints directly to the standard output and does not return the greeting string. If you need to store or manipulate the greeting message, you will need to modify the function to return a `String` instead. - The function will concatenate the provided `name` as-is. If an empty string is passed, the output will be "Hello, !". - If `null` is passed as the argument, Java's string concatenation will convert it to the string "null", resulting in the output "Hello, null!".</t>
         </is>
       </c>
     </row>
@@ -662,22 +662,22 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>The `main` function serves as the entry point for the Java application, demonstrating the functionality of the `add`, `factorial`, and `greet` methods by printing their results to the console.</t>
+          <t>The `main` function serves as the primary entry point for the Java application, executing a series of method calls to demonstrate the program's functionality.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>- `args`: `String[]` - An array of `String` objects that allows passing command-line arguments to the application. This parameter is not utilized within the body of this function.</t>
+          <t>Description | An array of `String` objects that holds any command-line arguments passed to the program upon execution. This parameter is not utilized within the current implementation. |</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>The `main` method is the starting point of execution for the Java program. When the program is run, the Java Virtual Machine (JVM) calls this method. The method performs the following operations in sequence: 1. It calls the `add(5, 10)` method to calculate the sum of two integers. The result is concatenated with the string `"Sum: "` and printed to the standard output console. 2. It calls the `factorial(5)` method to compute the factorial of the number 5. The result is then concatenated with t...</t>
+          <t>The `main` method is the starting point of execution for the program. Its logic proceeds as follows: 1. It first calls the static method `add(5, 10)` to calculate the sum of two integers. The result is concatenated with the string `"Sum: "` and printed to the standard console output. 2. Next, it calls the `factorial(5)` method to compute the factorial of the number 5. The returned value is then concatenated with the string `"Factorial: "` and displayed on the console. 3. Finally, it invokes t...</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>- The `main` method must have the exact signature `public static void main(String[] args)` to be recognized as the application's entry point by the JVM. - This method is not intended to be called directly from other parts of the code; it is invoked by the JVM when the program starts. - The `args` parameter can be used to provide configuration or data to the program at runtime from the command line, although it is unused in this specific implementation.</t>
+          <t>- This method has a specific signature (`public static void main(String[] args)`) that is recognized by the Java Virtual Machine (JVM) as the entry point of the application. - The program must be executed for this method to run; it is not intended to be called directly from other parts of the code. - The functionality demonstrated depends on the implementations of the `add`, `factorial`, and `greet` methods, which are called from within `main`.</t>
         </is>
       </c>
     </row>

--- a/main.xlsx
+++ b/main.xlsx
@@ -526,18 +526,18 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `Main` class serves as a container for several static utility methods and includes the main entry point for the Java application.</t>
+          <t>The `Main` class is a container for several static utility methods, including a function for addition, a recursive function for factorial calculation, and a procedure to print a greeting.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>The `Main` class is designed as a utility class containing static methods, meaning they can be called directly on the class without needing to create an instance. It demonstrates basic programming concepts through its methods and serves as the executable entry point for the program. The class includes the following static methods: **`public static int add(int a, int b)`** This method takes two integer parameters, `a` and `b`, and returns their sum. It performs a simple addition operation. **`...</t>
+          <t>The `Main` class provides a set of standalone, static methods that can be called without creating an instance of the class. It also contains the primary `main` method, which serves as the entry point for the Java application. The class includes the following methods: - `public static int add(int a, int b)`: This function takes two integer parameters, `a` and `b`, and returns their sum. - `public static int factorial(int n)`: This function calculates the factorial of a non-negative integer `n`...</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- All methods in this class are `static`, so they should be invoked directly on the class itself (e.g., `Main.add(x, y)`), not on an instance of the class. - The `factorial` method uses recursion. Providing a very large integer as input may lead to a `java.lang.StackOverflowError`. - The `main` method is the standard entry point for any Java application and is used here to demonstrate the functionality of the other methods.</t>
+          <t>- All methods in this class are `static`, meaning they should be called directly on the class itself (e.g., `Main.add(5, 10)`), and no object instantiation is required. - The `factorial` method is recursive. Inputting a very large number can lead to a `StackOverflowError`. - The `greet` method prints directly to the console and does not return a value.</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `add` function computes the sum of two integer numbers.</t>
+          <t>The `add` function calculates and returns the sum of two integer values.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -567,12 +567,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>The `add` function is a `public static` method that takes two integer parameters, `a` and `b`. It performs a standard arithmetic addition operation on these two integers. The core logic is simply `return a + b;`, which calculates the sum and immediately returns the resulting integer value. Because it is a `static` method, it can be called directly on the `Main` class without needing to create an object instance.</t>
+          <t>The `add` function is a `public static` method that performs a simple arithmetic addition. It takes two integer parameters, `a` and `b`. Inside the function, the addition operator (`+`) is used to compute the sum of these two numbers. The resulting integer value is then returned by the function. Because the method is `static`, it can be called directly on the `Main` class without needing to create an instance of the class.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- As a `static` method, it should be invoked using the class name, for example, `Main.add(5, 10)`. - The function operates on primitive `int` types. Be aware of potential integer overflow if the sum of `a` and `b` exceeds the maximum value for an `int` (`Integer.MAX_VALUE`) or falls below the minimum value (`Integer.MIN_VALUE`). - The function does not perform any null checks or input validation. **Output Example**: A single integer representing the sum. `15`</t>
+          <t>- This function is designed specifically for `int` data types. Providing arguments of other types will cause a compile-time error. - The return value is also an `int`. Be mindful of potential integer overflow if the sum of `a` and `b` exceeds the maximum value for an `int` (2,147,483,647). If an overflow occurs, the value will wrap around to the negative range. **Output Example**: A single integer representing the sum.</t>
         </is>
       </c>
     </row>
@@ -597,17 +597,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>- `n`: The non-negative integer for which the factorial will be calculated.</t>
+          <t>- `n` (int): The non-negative integer for which the factorial will be computed.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function computes the factorial of a number `n`, which is the product of all positive integers up to `n` (n!). It employs a recursive approach to solve the problem. The logic follows two main paths: 1. **Base Case**: If the input `n` is less than or equal to 1, the function returns `1`. This is because the factorial of 0 (0!) and 1 (1!) are both defined as 1. This condition serves as the termination point for the recursion. 2. **Recursive Step**: If `n` is greater than 1, the function re...</t>
+          <t>This function provides a classic recursive implementation to compute the factorial of a number `n` (denoted as `n!`). The logic follows the mathematical definition of a factorial: 1. **Base Case**: The factorial of 0 (`0!`) and 1 (`1!`) is 1. The function checks if the input `n` is less than or equal to 1. If it is, the function terminates the recursion and returns `1`. 2. **Recursive Step**: If `n` is greater than 1, the function multiplies `n` by the result of calling itself with the argume...</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- The function is intended for non-negative integers. Providing a negative integer will cause infinite recursion, leading to a `StackOverflowError`. - The return type is `int`. Factorial values grow very rapidly. The largest factorial that can be stored in a standard 32-bit signed `int` is `12!`. Any input greater than 12 will result in an integer overflow, producing an incorrect value. For larger numbers, a data type like `long` or `BigInteger` would be required. **Output Example**: A call t...</t>
+          <t>- This function is designed for non-negative integers. Passing a negative value for `n` will cause infinite recursion, leading to a `java.lang.StackOverflowError`. - The return type is `int`. Factorial values grow very quickly, and an integer overflow will occur for `n &gt; 12`. The result of an overflow will be an incorrect, often negative, value. For calculating factorials of larger numbers, consider using a data type with a larger range, such as `long` or `java.math.BigInteger`. **Output Exam...</t>
         </is>
       </c>
     </row>
@@ -627,22 +627,22 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>The `greet` function prints a personalized greeting message to the standard output console.</t>
+          <t>The `greet` function prints a personalized greeting message to the standard output.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>- `name` (String): The name of the person or entity to be greeted.</t>
+          <t>- `name`: `String` - The name of the person or entity to greet. This string will be incorporated into the output message.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>The `greet` function is a `public static` method, meaning it can be called directly on the `Main` class without needing to create an instance of the class. It is designed to perform a simple action: displaying a greeting. The function accepts a single parameter, `name`, which is a `String`. It then uses the `System.out.println()` method to print a formatted string to the console. The output string is constructed by concatenating the literal string `"Hello, "`, the value passed in the `name` p...</t>
+          <t>This `static` method provides a simple way to display a standardized greeting. It accepts a single `String` parameter, `name`. The core logic involves string concatenation: it combines the literal string `"Hello, "`, the value passed in the `name` parameter, and the literal string `"!"`. The resulting string is then printed to the standard console output using `System.out.println()`, which also appends a newline character at the end. Because the method is declared as `void`, it does not retur...</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>- This function prints directly to the standard output and does not return the greeting string. If you need to store or manipulate the greeting message, you will need to modify the function to return a `String` instead. - The function will concatenate the provided `name` as-is. If an empty string is passed, the output will be "Hello, !". - If `null` is passed as the argument, Java's string concatenation will convert it to the string "null", resulting in the output "Hello, null!".</t>
+          <t>- This is a `static` method and should be called on the class, for example, `Main.greet("World")`. - The method prints directly to the console; it does not return the greeting string. - If a `null` value is passed as the `name`, the output will be "Hello, null!".</t>
         </is>
       </c>
     </row>
@@ -662,22 +662,22 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>The `main` function serves as the primary entry point for the Java application, executing a series of method calls to demonstrate the program's functionality.</t>
+          <t>The `main` function serves as the entry point for the Java application, executing a sequence of calls to other methods and printing their results to the console.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Description | An array of `String` objects that holds any command-line arguments passed to the program upon execution. This parameter is not utilized within the current implementation. |</t>
+          <t>Description | An array of `String` objects that can hold command-line arguments passed to the application upon execution. This parameter is not utilized in this function's body. |</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>The `main` method is the starting point of execution for the program. Its logic proceeds as follows: 1. It first calls the static method `add(5, 10)` to calculate the sum of two integers. The result is concatenated with the string `"Sum: "` and printed to the standard console output. 2. Next, it calls the `factorial(5)` method to compute the factorial of the number 5. The returned value is then concatenated with the string `"Factorial: "` and displayed on the console. 3. Finally, it invokes t...</t>
+          <t>The `main` method is the starting point for the execution of the program. It is declared as `public` and `static`, meaning it can be called by the Java Virtual Machine (JVM) without creating an instance of the `Main` class. The method performs the following operations in sequence: 1. It calls the `add(5, 10)` method. The return value of this call is concatenated with the string `"Sum: "` and the entire resulting string is printed to the standard output console. 2. It calls the `factorial(5)` ...</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>- This method has a specific signature (`public static void main(String[] args)`) that is recognized by the Java Virtual Machine (JVM) as the entry point of the application. - The program must be executed for this method to run; it is not intended to be called directly from other parts of the code. - The functionality demonstrated depends on the implementations of the `add`, `factorial`, and `greet` methods, which are called from within `main`.</t>
+          <t>- The `main` method is a special method in Java that the JVM looks for as the starting point of any Java program. - The method signature must be `public static void main(String[] args)` for the application to be launchable. - This implementation depends on the existence of three other methods: `add(int, int)`, `factorial(int)`, and `greet(String)`. These methods must be defined within the `Main` class or be otherwise accessible at compile time.</t>
         </is>
       </c>
     </row>

--- a/main.xlsx
+++ b/main.xlsx
@@ -466,7 +466,7 @@
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
@@ -526,18 +526,18 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `Main` class is a container for several static utility methods, including a function for addition, a recursive function for factorial calculation, and a procedure to print a greeting.</t>
+          <t>The `Main` class serves as the entry point for the application and provides a collection of static utility methods for basic arithmetic, factorial calculation, and printing greetings.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>The `Main` class provides a set of standalone, static methods that can be called without creating an instance of the class. It also contains the primary `main` method, which serves as the entry point for the Java application. The class includes the following methods: - `public static int add(int a, int b)`: This function takes two integer parameters, `a` and `b`, and returns their sum. - `public static int factorial(int n)`: This function calculates the factorial of a non-negative integer `n`...</t>
+          <t>The `Main` class is a container for several independent, static helper functions and the primary `main` method which executes the program. **Methods:** - `public static int add(int a, int b)`: This function takes two integer arguments, `a` and `b`, and returns their sum. It performs a simple addition operation. - `public static int factorial(int n)`: This function calculates the factorial of a given non-negative integer `n` using recursion. - **Base Case**: If `n` is less than or equal to 1, ...</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- All methods in this class are `static`, meaning they should be called directly on the class itself (e.g., `Main.add(5, 10)`), and no object instantiation is required. - The `factorial` method is recursive. Inputting a very large number can lead to a `StackOverflowError`. - The `greet` method prints directly to the console and does not return a value.</t>
+          <t>- All methods in this class are `static` and should be invoked directly on the class, e.g., `Main.add(5, 3)`. There is no need to instantiate the `Main` class. - The `factorial` method is recursive. Providing a very large integer as input may lead to a `StackOverflowError`. - The `greet` method prints its output directly to the standard output (console) and does not return the greeting string.</t>
         </is>
       </c>
     </row>
@@ -552,27 +552,27 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>add</t>
+          <t>add(a, b)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `add` function calculates and returns the sum of two integer values.</t>
+          <t>The `add` function computes the sum of two integer numbers.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Description | The first integer to be added. | The second integer to be added. |</t>
+          <t>Description | The first integer operand to be added. | The second integer operand to be added. |</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>The `add` function is a `public static` method that performs a simple arithmetic addition. It takes two integer parameters, `a` and `b`. Inside the function, the addition operator (`+`) is used to compute the sum of these two numbers. The resulting integer value is then returned by the function. Because the method is `static`, it can be called directly on the `Main` class without needing to create an instance of the class.</t>
+          <t>The `add` function is a `public static` method that takes two integer parameters, `a` and `b`. The core logic of the function is to perform a standard arithmetic addition operation on these two integers. The expression `a + b` calculates their sum. The resulting integer value is then returned by the function. Because it is a `static` method, it can be called directly on the `Main` class without needing to create an instance of the class.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- This function is designed specifically for `int` data types. Providing arguments of other types will cause a compile-time error. - The return value is also an `int`. Be mindful of potential integer overflow if the sum of `a` and `b` exceeds the maximum value for an `int` (2,147,483,647). If an overflow occurs, the value will wrap around to the negative range. **Output Example**: A single integer representing the sum.</t>
+          <t>- As a `static` method, it should be invoked directly on the class, for example, `Main.add(5, 10)`. - The function operates within the standard range of a Java `int`. If the sum of `a` and `b` exceeds `Integer.MAX_VALUE` or is less than `Integer.MIN_VALUE`, an integer overflow will occur, and the result will wrap around. - The function only accepts `int` types. Passing other numeric types will require an explicit cast to `int`. **Output Example**: The function returns a single integer value r...</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>factorial</t>
+          <t>factorial(n)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function provides a classic recursive implementation to compute the factorial of a number `n` (denoted as `n!`). The logic follows the mathematical definition of a factorial: 1. **Base Case**: The factorial of 0 (`0!`) and 1 (`1!`) is 1. The function checks if the input `n` is less than or equal to 1. If it is, the function terminates the recursion and returns `1`. 2. **Recursive Step**: If `n` is greater than 1, the function multiplies `n` by the result of calling itself with the argume...</t>
+          <t>This function implements the mathematical factorial operation using recursion. The factorial of a non-negative integer `n`, denoted by `n!`, is the product of all positive integers less than or equal to `n`. The logic follows two main paths: 1. **Base Case**: If the input `n` is less than or equal to 1 (i.e., 0 or 1), the function returns `1`. This is because `0!` and `1!` are both defined as 1, and this condition serves as the termination point for the recursion. 2. **Recursive Step**: If `n...</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- This function is designed for non-negative integers. Passing a negative value for `n` will cause infinite recursion, leading to a `java.lang.StackOverflowError`. - The return type is `int`. Factorial values grow very quickly, and an integer overflow will occur for `n &gt; 12`. The result of an overflow will be an incorrect, often negative, value. For calculating factorials of larger numbers, consider using a data type with a larger range, such as `long` or `java.math.BigInteger`. **Output Exam...</t>
+          <t>- This function is intended for non-negative integers. Providing a negative number will lead to infinite recursion and result in a `StackOverflowError`. - Due to the recursive implementation, very large values of `n` can also cause a `StackOverflowError` by exceeding the call stack depth limit. - The return type is `int`. Factorials grow very rapidly, and the result will overflow the standard 32-bit `int` data type for `n &gt; 12`. For larger numbers, a `long` or `java.math.BigInteger` implement...</t>
         </is>
       </c>
     </row>
@@ -622,27 +622,27 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>greet</t>
+          <t>greet(name)</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>The `greet` function prints a personalized greeting message to the standard output.</t>
+          <t>The `greet` function prints a personalized greeting message to the standard output console.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>- `name`: `String` - The name of the person or entity to greet. This string will be incorporated into the output message.</t>
+          <t>- `name` (String): The name to be included in the greeting message.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>This `static` method provides a simple way to display a standardized greeting. It accepts a single `String` parameter, `name`. The core logic involves string concatenation: it combines the literal string `"Hello, "`, the value passed in the `name` parameter, and the literal string `"!"`. The resulting string is then printed to the standard console output using `System.out.println()`, which also appends a newline character at the end. Because the method is declared as `void`, it does not retur...</t>
+          <t>This static function provides a simple way to display a standardized greeting. It takes a single `String` argument, `name`. The core logic involves string concatenation: it combines the literal string `"Hello, "`, the value passed in the `name` parameter, and the literal string `"!"`. This complete string is then passed to the `System.out.println()` method, which prints the message to the console and appends a newline character. For example, if the `name` parameter is `"World"`, the function ...</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>- This is a `static` method and should be called on the class, for example, `Main.greet("World")`. - The method prints directly to the console; it does not return the greeting string. - If a `null` value is passed as the `name`, the output will be "Hello, null!".</t>
+          <t>- This is a `static` method, so it should be called directly on the `Main` class, like `Main.greet("Alice")`. - The function has a `void` return type, meaning it does not return any value. Its only effect is printing to the console. - If `null` is passed as the argument, the output will be "Hello, null!".</t>
         </is>
       </c>
     </row>
@@ -657,27 +657,27 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>main(args)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>The `main` function serves as the entry point for the Java application, executing a sequence of calls to other methods and printing their results to the console.</t>
+          <t>The `main` function serves as the primary entry point for the Java application, demonstrating the functionality of other methods within the class by calling them with predefined values and printing the results to the console.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Description | An array of `String` objects that can hold command-line arguments passed to the application upon execution. This parameter is not utilized in this function's body. |</t>
+          <t>Description | An array of strings that accepts command-line arguments passed to the program at runtime. This parameter is not utilized within the current implementation of the method. |</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>The `main` method is the starting point for the execution of the program. It is declared as `public` and `static`, meaning it can be called by the Java Virtual Machine (JVM) without creating an instance of the `Main` class. The method performs the following operations in sequence: 1. It calls the `add(5, 10)` method. The return value of this call is concatenated with the string `"Sum: "` and the entire resulting string is printed to the standard output console. 2. It calls the `factorial(5)` ...</t>
+          <t>The `main` method is the starting point of execution for the Java program. The Java Virtual Machine (JVM) invokes this method when the program is run. The method is declared as `public` and `static`, allowing it to be called without creating an instance of the `Main` class. The method's execution flow is as follows: 1. It first calls the `add(5, 10)` method. The return value (the sum of 5 and 10) is concatenated with the string `"Sum: "` and printed to the standard output console. 2. Next, it...</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>- The `main` method is a special method in Java that the JVM looks for as the starting point of any Java program. - The method signature must be `public static void main(String[] args)` for the application to be launchable. - This implementation depends on the existence of three other methods: `add(int, int)`, `factorial(int)`, and `greet(String)`. These methods must be defined within the `Main` class or be otherwise accessible at compile time.</t>
+          <t>- This method is the designated entry point for the application and is automatically called by the JVM. It should not be called directly from other parts of the code. - The functionality of this method is dependent on the `add`, `factorial`, and `greet` methods being defined and accessible within the same scope. - While the `args` parameter is defined, it is not used in this specific implementation. However, it can be used to pass external data to the application from the command line.</t>
         </is>
       </c>
     </row>

--- a/main.xlsx
+++ b/main.xlsx
@@ -526,18 +526,18 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `Main` class serves as the entry point for the application and provides a collection of static utility methods for basic arithmetic, factorial calculation, and printing greetings.</t>
+          <t>The `Main` class serves as the primary entry point for the Java application and contains a collection of static utility methods for performing basic calculations and printing messages.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>The `Main` class is a container for several independent, static helper functions and the primary `main` method which executes the program. **Methods:** - `public static int add(int a, int b)`: This function takes two integer arguments, `a` and `b`, and returns their sum. It performs a simple addition operation. - `public static int factorial(int n)`: This function calculates the factorial of a given non-negative integer `n` using recursion. - **Base Case**: If `n` is less than or equal to 1, ...</t>
+          <t>The `Main` class is a container for several independent, static methods and the `main` method, which orchestrates the execution of the program. **Methods:** - `public static int add(int a, int b)`: This function takes two integer arguments, `a` and `b`, and returns their sum. It performs a simple addition operation. - `public static int factorial(int n)`: This function calculates the factorial of a non-negative integer `n` using recursion. - The base case for the recursion is when `n` is less...</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- All methods in this class are `static` and should be invoked directly on the class, e.g., `Main.add(5, 3)`. There is no need to instantiate the `Main` class. - The `factorial` method is recursive. Providing a very large integer as input may lead to a `StackOverflowError`. - The `greet` method prints its output directly to the standard output (console) and does not return the greeting string.</t>
+          <t>- All methods in this class are `static`, meaning they belong to the class itself and can be called directly using the class name (e.g., `Main.add(5, 10)`) without needing to create an instance of the `Main` class. - The `factorial` method is recursive. Providing a very large integer as input may result in a `StackOverflowError` due to excessive recursion depth. - The `greet` method prints directly to the console and has a `void` return type, so it cannot be used in an expression to assign a ...</t>
         </is>
       </c>
     </row>
@@ -557,22 +557,22 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `add` function computes the sum of two integer numbers.</t>
+          <t>The `add` function calculates the sum of two integer values.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Description | The first integer operand to be added. | The second integer operand to be added. |</t>
+          <t>Description | The first integer operand. | The second integer operand. |</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>The `add` function is a `public static` method that takes two integer parameters, `a` and `b`. The core logic of the function is to perform a standard arithmetic addition operation on these two integers. The expression `a + b` calculates their sum. The resulting integer value is then returned by the function. Because it is a `static` method, it can be called directly on the `Main` class without needing to create an instance of the class.</t>
+          <t>This `static` function provides a straightforward implementation of integer addition. It accepts two integer arguments, `a` and `b`. The core logic uses the standard arithmetic addition operator (`+`) to compute the sum of these two numbers. The function then returns the resulting integer value.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- As a `static` method, it should be invoked directly on the class, for example, `Main.add(5, 10)`. - The function operates within the standard range of a Java `int`. If the sum of `a` and `b` exceeds `Integer.MAX_VALUE` or is less than `Integer.MIN_VALUE`, an integer overflow will occur, and the result will wrap around. - The function only accepts `int` types. Passing other numeric types will require an explicit cast to `int`. **Output Example**: The function returns a single integer value r...</t>
+          <t>- As a `static` method, it should be called on the class itself, not on an instance of the class (e.g., `Main.add(5, 10)`). - Users should be aware of potential integer overflow. If the sum of `a` and `b` exceeds the maximum value of an `int` (`Integer.MAX_VALUE`) or is less than the minimum value (`Integer.MIN_VALUE`), the result will wrap around according to Java's two's complement arithmetic. **Output Example**: The function returns a single `int` value representing the sum. For an input o...</t>
         </is>
       </c>
     </row>
@@ -597,17 +597,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>- `n` (int): The non-negative integer for which the factorial will be computed.</t>
+          <t>- **`n`** (int): The non-negative integer for which the factorial will be computed.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function implements the mathematical factorial operation using recursion. The factorial of a non-negative integer `n`, denoted by `n!`, is the product of all positive integers less than or equal to `n`. The logic follows two main paths: 1. **Base Case**: If the input `n` is less than or equal to 1 (i.e., 0 or 1), the function returns `1`. This is because `0!` and `1!` are both defined as 1, and this condition serves as the termination point for the recursion. 2. **Recursive Step**: If `n...</t>
+          <t>This function implements the factorial calculation using a recursive approach. The logic is divided into two main parts: 1. **Base Case**: The recursion terminates when the input `n` is less than or equal to `1`. In mathematics, the factorial of 0 (`0!`) and 1 (`1!`) are both defined as `1`. The function handles this by returning `1` directly, which prevents an infinite loop. 2. **Recursive Step**: If `n` is greater than `1`, the function multiplies `n` by the result of calling itself with th...</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- This function is intended for non-negative integers. Providing a negative number will lead to infinite recursion and result in a `StackOverflowError`. - Due to the recursive implementation, very large values of `n` can also cause a `StackOverflowError` by exceeding the call stack depth limit. - The return type is `int`. Factorials grow very rapidly, and the result will overflow the standard 32-bit `int` data type for `n &gt; 12`. For larger numbers, a `long` or `java.math.BigInteger` implement...</t>
+          <t>- The function is intended for non-negative integers. Providing a negative number will lead to infinite recursion, resulting in a `StackOverflowError`. - The return type is `int`. Factorial values grow very quickly. The maximum value for a standard 32-bit signed integer in Java is `2,147,483,647`. The largest factorial that can be stored in an `int` is `12!`. Any input `n &gt; 12` will cause an integer overflow, leading to an incorrect result. - The function correctly handles `factorial(0)` and ...</t>
         </is>
       </c>
     </row>
@@ -627,22 +627,22 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>The `greet` function prints a personalized greeting message to the standard output console.</t>
+          <t>The `greet` function prints a personalized greeting message to the standard console output.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>- `name` (String): The name to be included in the greeting message.</t>
+          <t>- `name`: (String) The name to be included in the greeting message.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>This static function provides a simple way to display a standardized greeting. It takes a single `String` argument, `name`. The core logic involves string concatenation: it combines the literal string `"Hello, "`, the value passed in the `name` parameter, and the literal string `"!"`. This complete string is then passed to the `System.out.println()` method, which prints the message to the console and appends a newline character. For example, if the `name` parameter is `"World"`, the function ...</t>
+          <t>This `public static` method provides a simple way to display a greeting. It is accessible from anywhere in the project and can be called directly on the `Main` class without needing to create an instance of it. The function takes a single `String` parameter, `name`. It then constructs a new string by concatenating the literal string `"Hello, "`, the value of the `name` parameter, and the literal string `"!"`. Finally, it uses the `System.out.println()` method to print the resulting string to ...</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>- This is a `static` method, so it should be called directly on the `Main` class, like `Main.greet("Alice")`. - The function has a `void` return type, meaning it does not return any value. Its only effect is printing to the console. - If `null` is passed as the argument, the output will be "Hello, null!".</t>
+          <t>- This function prints directly to the console and does not return the greeting string. If you need to manipulate the string itself, the function would need to be modified to return a `String` instead of being `void`. - The method is `static`, so it should be called using the class name: `Main.greet("your_name");`. - Passing `null` as the `name` argument will not cause an error but will result in the output "Hello, null!".</t>
         </is>
       </c>
     </row>
@@ -662,22 +662,22 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>The `main` function serves as the primary entry point for the Java application, demonstrating the functionality of other methods within the class by calling them with predefined values and printing the results to the console.</t>
+          <t>The `main` function serves as the primary entry point for the Java application, executing a series of predefined method calls to demonstrate their functionality.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Description | An array of strings that accepts command-line arguments passed to the program at runtime. This parameter is not utilized within the current implementation of the method. |</t>
+          <t>Description | An array of strings that holds command-line arguments passed to the application at runtime. This parameter is not utilized in the current implementation. |</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>The `main` method is the starting point of execution for the Java program. The Java Virtual Machine (JVM) invokes this method when the program is run. The method is declared as `public` and `static`, allowing it to be called without creating an instance of the `Main` class. The method's execution flow is as follows: 1. It first calls the `add(5, 10)` method. The return value (the sum of 5 and 10) is concatenated with the string `"Sum: "` and printed to the standard output console. 2. Next, it...</t>
+          <t>As the standard entry point for a Java program, the `main` function is executed automatically when the application starts. Its logic proceeds in three distinct steps: 1. It first calls the `add(5, 10)` method to calculate the sum of two integers. The result is then concatenated with the string `"Sum: "` and printed to the standard output console. 2. Next, it calls the `factorial(5)` method to compute the factorial of the number 5. The returned value is concatenated with the string `"Factorial...</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>- This method is the designated entry point for the application and is automatically called by the JVM. It should not be called directly from other parts of the code. - The functionality of this method is dependent on the `add`, `factorial`, and `greet` methods being defined and accessible within the same scope. - While the `args` parameter is defined, it is not used in this specific implementation. However, it can be used to pass external data to the application from the command line.</t>
+          <t>- This method signature (`public static void main(String[] args)`) is the mandatory entry point for any executable Java class. - The `args` parameter allows for passing configuration or data to the program from the command line, although it is not used in this specific code. - The primary purpose of this `main` function is to demonstrate the functionality of the `add`, `factorial`, and `greet` methods.</t>
         </is>
       </c>
     </row>

--- a/main.xlsx
+++ b/main.xlsx
@@ -467,10 +467,10 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -524,22 +524,10 @@
           <t>Main</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>The `Main` class serves as the primary entry point for the Java application and contains a collection of static utility methods for performing basic calculations and printing messages.</t>
-        </is>
-      </c>
+      <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>The `Main` class is a container for several independent, static methods and the `main` method, which orchestrates the execution of the program. **Methods:** - `public static int add(int a, int b)`: This function takes two integer arguments, `a` and `b`, and returns their sum. It performs a simple addition operation. - `public static int factorial(int n)`: This function calculates the factorial of a non-negative integer `n` using recursion. - The base case for the recursion is when `n` is less...</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>- All methods in this class are `static`, meaning they belong to the class itself and can be called directly using the class name (e.g., `Main.add(5, 10)`) without needing to create an instance of the `Main` class. - The `factorial` method is recursive. Providing a very large integer as input may result in a `StackOverflowError` due to excessive recursion depth. - The `greet` method prints directly to the console and has a `void` return type, so it cannot be used in an expression to assign a ...</t>
-        </is>
-      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="4" t="n">
@@ -555,26 +543,10 @@
           <t>add(a, b)</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>The `add` function calculates the sum of two integer values.</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Description | The first integer operand. | The second integer operand. |</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>This `static` function provides a straightforward implementation of integer addition. It accepts two integer arguments, `a` and `b`. The core logic uses the standard arithmetic addition operator (`+`) to compute the sum of these two numbers. The function then returns the resulting integer value.</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>- As a `static` method, it should be called on the class itself, not on an instance of the class (e.g., `Main.add(5, 10)`). - Users should be aware of potential integer overflow. If the sum of `a` and `b` exceeds the maximum value of an `int` (`Integer.MAX_VALUE`) or is less than the minimum value (`Integer.MIN_VALUE`), the result will wrap around according to Java's two's complement arithmetic. **Output Example**: The function returns a single `int` value representing the sum. For an input o...</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="inlineStr"/>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -590,26 +562,10 @@
           <t>factorial(n)</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>The `factorial` function recursively calculates the factorial of a given non-negative integer.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>- **`n`** (int): The non-negative integer for which the factorial will be computed.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>This function implements the factorial calculation using a recursive approach. The logic is divided into two main parts: 1. **Base Case**: The recursion terminates when the input `n` is less than or equal to `1`. In mathematics, the factorial of 0 (`0!`) and 1 (`1!`) are both defined as `1`. The function handles this by returning `1` directly, which prevents an infinite loop. 2. **Recursive Step**: If `n` is greater than `1`, the function multiplies `n` by the result of calling itself with th...</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>- The function is intended for non-negative integers. Providing a negative number will lead to infinite recursion, resulting in a `StackOverflowError`. - The return type is `int`. Factorial values grow very quickly. The maximum value for a standard 32-bit signed integer in Java is `2,147,483,647`. The largest factorial that can be stored in an `int` is `12!`. Any input `n &gt; 12` will cause an integer overflow, leading to an incorrect result. - The function correctly handles `factorial(0)` and ...</t>
-        </is>
-      </c>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="4" t="n">
@@ -625,26 +581,10 @@
           <t>greet(name)</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>The `greet` function prints a personalized greeting message to the standard console output.</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>- `name`: (String) The name to be included in the greeting message.</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>This `public static` method provides a simple way to display a greeting. It is accessible from anywhere in the project and can be called directly on the `Main` class without needing to create an instance of it. The function takes a single `String` parameter, `name`. It then constructs a new string by concatenating the literal string `"Hello, "`, the value of the `name` parameter, and the literal string `"!"`. Finally, it uses the `System.out.println()` method to print the resulting string to ...</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>- This function prints directly to the console and does not return the greeting string. If you need to manipulate the string itself, the function would need to be modified to return a `String` instead of being `void`. - The method is `static`, so it should be called using the class name: `Main.greet("your_name");`. - Passing `null` as the `name` argument will not cause an error but will result in the output "Hello, null!".</t>
-        </is>
-      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -660,26 +600,10 @@
           <t>main(args)</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>The `main` function serves as the primary entry point for the Java application, executing a series of predefined method calls to demonstrate their functionality.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Description | An array of strings that holds command-line arguments passed to the application at runtime. This parameter is not utilized in the current implementation. |</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>As the standard entry point for a Java program, the `main` function is executed automatically when the application starts. Its logic proceeds in three distinct steps: 1. It first calls the `add(5, 10)` method to calculate the sum of two integers. The result is then concatenated with the string `"Sum: "` and printed to the standard output console. 2. Next, it calls the `factorial(5)` method to compute the factorial of the number 5. The returned value is concatenated with the string `"Factorial...</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>- This method signature (`public static void main(String[] args)`) is the mandatory entry point for any executable Java class. - The `args` parameter allows for passing configuration or data to the program from the command line, although it is not used in this specific code. - The primary purpose of this `main` function is to demonstrate the functionality of the `add`, `factorial`, and `greet` methods.</t>
-        </is>
-      </c>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
